--- a/JsonConverter/ExcelFiles/GroundPositionData.xlsx
+++ b/JsonConverter/ExcelFiles/GroundPositionData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,15 +19,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ground_position_mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ground_position_guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ground_position_halfguard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>ground_position_backcontrol</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionSuccessMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundEscapeSuccessMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionEntrySuccessMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrikeDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Position</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -801,10 +846,11 @@
   <x:dimension ref="A1:H35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="28" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="41.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="6" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="26.14453125" style="1" customWidth="1"/>
+    <x:col min="5" max="6" width="28.28515625" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="30.54296875" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="26.54296875" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
@@ -816,36 +862,129 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="C5" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D5" s="1">
+        <x:v>0.90000000000000002</x:v>
+      </x:c>
+      <x:c r="E5" s="1">
+        <x:v>0.84999999999999998</x:v>
+      </x:c>
+      <x:c r="F5" s="1">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:2" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="2"/>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="H4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5"/>
+    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A6" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="1">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D6" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E6" s="1">
+        <x:v>0.45000000000000001</x:v>
+      </x:c>
+      <x:c r="F6" s="1">
+        <x:v>0.69999999999999996</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="1">
+        <x:v>0.69999999999999996</x:v>
+      </x:c>
+      <x:c r="D7" s="1">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E7" s="1">
+        <x:v>0.29999999999999999</x:v>
+      </x:c>
+      <x:c r="F7" s="1">
+        <x:v>1.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A8" s="5"/>

--- a/JsonConverter/ExcelFiles/GroundPositionData.xlsx
+++ b/JsonConverter/ExcelFiles/GroundPositionData.xlsx
@@ -19,9 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <x:si>
-    <x:t>float</x:t>
+    <x:t>ground_position_mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ground_position_guard</x:t>
   </x:si>
   <x:si>
     <x:t>BackControl</x:t>
@@ -30,22 +33,25 @@
     <x:t>HalfGuard</x:t>
   </x:si>
   <x:si>
-    <x:t>Mount</x:t>
+    <x:t>Position</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrikeDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PositionEntrySuccessMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundEscapeSuccessMultiplier</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>ground_position_mount</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>ground_position_guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ground_position_halfguard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
+    <x:t>Mount</x:t>
   </x:si>
   <x:si>
     <x:t>고유 ID</x:t>
@@ -54,25 +60,22 @@
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>ground_position_backcontrol</x:t>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>SubmissionSuccessMultiplier</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundEscapeSuccessMultiplier</x:t>
+    <x:t>ground_position_backcontrol</x:t>
   </x:si>
   <x:si>
-    <x:t>PositionEntrySuccessMultiplier</x:t>
+    <x:t>ground_position_halfguard</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundStrikeDamageMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Position</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>BottomStaminaLossPerSecond</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -862,55 +865,61 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="C3" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>12</x:v>
+      <x:c r="G3" s="7" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1</x:v>
@@ -924,14 +933,17 @@
       <x:c r="F4" s="1">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="G4" s="1">
+        <x:v>0.20000000000000001</x:v>
+      </x:c>
       <x:c r="H4" s="4"/>
     </x:row>
-    <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>0.5</x:v>
@@ -945,13 +957,16 @@
       <x:c r="F5" s="1">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="G5" s="1">
+        <x:v>0.40000000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>1.5</x:v>
@@ -965,13 +980,16 @@
       <x:c r="F6" s="1">
         <x:v>0.69999999999999996</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="G6" s="1">
+        <x:v>0.69999999999999996</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>0.69999999999999996</x:v>
@@ -984,6 +1002,9 @@
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G7" s="1">
+        <x:v>1.2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2" ht="15.75" customHeight="1">
